--- a/Database/Table/Boost.xlsx
+++ b/Database/Table/Boost.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyProjects\Ju.GundamWars\Database\Table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{072FCDF6-D0D4-4EBD-9B51-E64B4616A191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09C90C36-C4BD-4535-AD27-045B508B88E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14370" yWindow="0" windowWidth="14430" windowHeight="15600" activeTab="2" xr2:uid="{2B7B1DB3-ED5C-41A5-9C29-22C9C7198DDD}"/>
+    <workbookView xWindow="14370" yWindow="0" windowWidth="14430" windowHeight="15600" tabRatio="677" activeTab="3" xr2:uid="{2B7B1DB3-ED5C-41A5-9C29-22C9C7198DDD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="PilotAbility" sheetId="2" r:id="rId2"/>
     <sheet name="SupportBadge" sheetId="3" r:id="rId3"/>
+    <sheet name="SupportSlot" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$36</definedName>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="123">
   <si>
     <t>機体</t>
   </si>
@@ -358,6 +359,60 @@
   </si>
   <si>
     <t>45</t>
+  </si>
+  <si>
+    <t>Kind</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>1400</t>
+  </si>
+  <si>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>0.3</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>0.5</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>6.5</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>1200</t>
   </si>
 </sst>
 </file>
@@ -789,7 +844,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91D87FBD-6B16-464F-926C-B79604E89A98}">
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.33203125" bestFit="1" customWidth="1"/>
@@ -1506,6 +1561,20 @@
       </c>
       <c r="F36">
         <v>13</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B37">
+        <v>16384</v>
+      </c>
+      <c r="C37" t="s">
+        <v>44</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1564,7 +1633,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="6" t="str">
-        <f>IF(E2=1,J2,J2*1000)</f>
+        <f t="shared" ref="F2:F33" si="0">IF(E2=1,J2,J2*1000)</f>
         <v>10</v>
       </c>
       <c r="G2" s="2">
@@ -1596,7 +1665,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="6" t="str">
-        <f>IF(E3=1,J3,J3*1000)</f>
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
       <c r="G3" s="2">
@@ -1628,7 +1697,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="6" t="str">
-        <f>IF(E4=1,J4,J4*1000)</f>
+        <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="G4" s="2">
@@ -1660,7 +1729,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="6" t="str">
-        <f>IF(E5=1,J5,J5*1000)</f>
+        <f t="shared" si="0"/>
         <v>200</v>
       </c>
       <c r="G5" s="2">
@@ -1692,7 +1761,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="6" t="str">
-        <f>IF(E6=1,J6,J6*1000)</f>
+        <f t="shared" si="0"/>
         <v>500</v>
       </c>
       <c r="G6" s="2">
@@ -1724,7 +1793,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="6" t="str">
-        <f>IF(E7=1,J7,J7*1000)</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="G7" s="2">
@@ -1756,7 +1825,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="6" t="str">
-        <f>IF(E8=1,J8,J8*1000)</f>
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
       <c r="G8" s="2">
@@ -1788,7 +1857,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="6" t="str">
-        <f>IF(E9=1,J9,J9*1000)</f>
+        <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="G9" s="2">
@@ -1820,7 +1889,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="6" t="str">
-        <f>IF(E10=1,J10,J10*1000)</f>
+        <f t="shared" si="0"/>
         <v>200</v>
       </c>
       <c r="G10" s="2">
@@ -1852,7 +1921,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="6" t="str">
-        <f>IF(E11=1,J11,J11*1000)</f>
+        <f t="shared" si="0"/>
         <v>500</v>
       </c>
       <c r="G11" s="2">
@@ -1884,7 +1953,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="6" t="str">
-        <f>IF(E12=1,J12,J12*1000)</f>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="G12" s="2">
@@ -1916,7 +1985,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="6" t="str">
-        <f>IF(E13=1,J13,J13*1000)</f>
+        <f t="shared" si="0"/>
         <v>75</v>
       </c>
       <c r="G13" s="2">
@@ -1948,7 +2017,7 @@
         <v>1</v>
       </c>
       <c r="F14" s="6" t="str">
-        <f>IF(E14=1,J14,J14*1000)</f>
+        <f t="shared" si="0"/>
         <v>150</v>
       </c>
       <c r="G14" s="2">
@@ -1980,7 +2049,7 @@
         <v>1</v>
       </c>
       <c r="F15" s="6" t="str">
-        <f>IF(E15=1,J15,J15*1000)</f>
+        <f t="shared" si="0"/>
         <v>300</v>
       </c>
       <c r="G15" s="2">
@@ -2012,7 +2081,7 @@
         <v>1</v>
       </c>
       <c r="F16" s="6" t="str">
-        <f>IF(E16=1,J16,J16*1000)</f>
+        <f t="shared" si="0"/>
         <v>750</v>
       </c>
       <c r="G16" s="2">
@@ -2044,7 +2113,7 @@
         <v>1</v>
       </c>
       <c r="F17" s="6" t="str">
-        <f>IF(E17=1,J17,J17*1000)</f>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="G17" s="2">
@@ -2076,7 +2145,7 @@
         <v>1</v>
       </c>
       <c r="F18" s="6" t="str">
-        <f>IF(E18=1,J18,J18*1000)</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="G18" s="2">
@@ -2108,7 +2177,7 @@
         <v>1</v>
       </c>
       <c r="F19" s="6" t="str">
-        <f>IF(E19=1,J19,J19*1000)</f>
+        <f t="shared" si="0"/>
         <v>60</v>
       </c>
       <c r="G19" s="2">
@@ -2140,7 +2209,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="6" t="str">
-        <f>IF(E20=1,J20,J20*1000)</f>
+        <f t="shared" si="0"/>
         <v>120</v>
       </c>
       <c r="G20" s="2">
@@ -2172,7 +2241,7 @@
         <v>1</v>
       </c>
       <c r="F21" s="6" t="str">
-        <f>IF(E21=1,J21,J21*1000)</f>
+        <f t="shared" si="0"/>
         <v>240</v>
       </c>
       <c r="G21" s="2">
@@ -2204,7 +2273,7 @@
         <v>1</v>
       </c>
       <c r="F22" s="6" t="str">
-        <f>IF(E22=1,J22,J22*1000)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="G22" s="2">
@@ -2236,7 +2305,7 @@
         <v>1</v>
       </c>
       <c r="F23" s="6" t="str">
-        <f>IF(E23=1,J23,J23*1000)</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="G23" s="2">
@@ -2268,7 +2337,7 @@
         <v>1</v>
       </c>
       <c r="F24" s="6" t="str">
-        <f>IF(E24=1,J24,J24*1000)</f>
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
       <c r="G24" s="2">
@@ -2300,7 +2369,7 @@
         <v>1</v>
       </c>
       <c r="F25" s="6" t="str">
-        <f>IF(E25=1,J25,J25*1000)</f>
+        <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="G25" s="2">
@@ -2332,7 +2401,7 @@
         <v>1</v>
       </c>
       <c r="F26" s="6" t="str">
-        <f>IF(E26=1,J26,J26*1000)</f>
+        <f t="shared" si="0"/>
         <v>200</v>
       </c>
       <c r="G26" s="2">
@@ -2364,7 +2433,7 @@
         <v>1</v>
       </c>
       <c r="F27" s="6" t="str">
-        <f>IF(E27=1,J27,J27*1000)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="G27" s="2">
@@ -2396,7 +2465,7 @@
         <v>1</v>
       </c>
       <c r="F28" s="6" t="str">
-        <f>IF(E28=1,J28,J28*1000)</f>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="G28" s="2">
@@ -2428,7 +2497,7 @@
         <v>1</v>
       </c>
       <c r="F29" s="6" t="str">
-        <f>IF(E29=1,J29,J29*1000)</f>
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
       <c r="G29" s="2">
@@ -2460,7 +2529,7 @@
         <v>1</v>
       </c>
       <c r="F30" s="6" t="str">
-        <f>IF(E30=1,J30,J30*1000)</f>
+        <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="G30" s="2">
@@ -2492,7 +2561,7 @@
         <v>1</v>
       </c>
       <c r="F31" s="6" t="str">
-        <f>IF(E31=1,J31,J31*1000)</f>
+        <f t="shared" si="0"/>
         <v>250</v>
       </c>
       <c r="G31" s="2">
@@ -2524,7 +2593,7 @@
         <v>2</v>
       </c>
       <c r="F32" s="6">
-        <f>IF(E32=1,J32,J32*1000)</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="G32" s="2">
@@ -2556,7 +2625,7 @@
         <v>2</v>
       </c>
       <c r="F33" s="6">
-        <f>IF(E33=1,J33,J33*1000)</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="G33" s="2">
@@ -2588,7 +2657,7 @@
         <v>2</v>
       </c>
       <c r="F34" s="6">
-        <f>IF(E34=1,J34,J34*1000)</f>
+        <f t="shared" ref="F34:F65" si="1">IF(E34=1,J34,J34*1000)</f>
         <v>50</v>
       </c>
       <c r="G34" s="2">
@@ -2620,7 +2689,7 @@
         <v>2</v>
       </c>
       <c r="F35" s="6">
-        <f>IF(E35=1,J35,J35*1000)</f>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="G35" s="2">
@@ -2652,7 +2721,7 @@
         <v>2</v>
       </c>
       <c r="F36" s="6">
-        <f>IF(E36=1,J36,J36*1000)</f>
+        <f t="shared" si="1"/>
         <v>200</v>
       </c>
       <c r="G36" s="2">
@@ -2684,7 +2753,7 @@
         <v>2</v>
       </c>
       <c r="F37" s="6">
-        <f>IF(E37=1,J37,J37*1000)</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="G37" s="2">
@@ -2716,7 +2785,7 @@
         <v>2</v>
       </c>
       <c r="F38" s="6">
-        <f>IF(E38=1,J38,J38*1000)</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="G38" s="2">
@@ -2748,7 +2817,7 @@
         <v>2</v>
       </c>
       <c r="F39" s="6">
-        <f>IF(E39=1,J39,J39*1000)</f>
+        <f t="shared" si="1"/>
         <v>30</v>
       </c>
       <c r="G39" s="2">
@@ -2780,7 +2849,7 @@
         <v>2</v>
       </c>
       <c r="F40" s="6">
-        <f>IF(E40=1,J40,J40*1000)</f>
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
       <c r="G40" s="2">
@@ -2812,7 +2881,7 @@
         <v>2</v>
       </c>
       <c r="F41" s="6">
-        <f>IF(E41=1,J41,J41*1000)</f>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="G41" s="2">
@@ -2844,7 +2913,7 @@
         <v>2</v>
       </c>
       <c r="F42" s="6">
-        <f>IF(E42=1,J42,J42*1000)</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="G42" s="2">
@@ -2876,7 +2945,7 @@
         <v>2</v>
       </c>
       <c r="F43" s="6">
-        <f>IF(E43=1,J43,J43*1000)</f>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="G43" s="2">
@@ -2908,7 +2977,7 @@
         <v>2</v>
       </c>
       <c r="F44" s="6">
-        <f>IF(E44=1,J44,J44*1000)</f>
+        <f t="shared" si="1"/>
         <v>60</v>
       </c>
       <c r="G44" s="2">
@@ -2940,7 +3009,7 @@
         <v>2</v>
       </c>
       <c r="F45" s="6">
-        <f>IF(E45=1,J45,J45*1000)</f>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="G45" s="2">
@@ -2972,7 +3041,7 @@
         <v>2</v>
       </c>
       <c r="F46" s="6">
-        <f>IF(E46=1,J46,J46*1000)</f>
+        <f t="shared" si="1"/>
         <v>200</v>
       </c>
       <c r="G46" s="2">
@@ -3004,7 +3073,7 @@
         <v>2</v>
       </c>
       <c r="F47" s="6">
-        <f>IF(E47=1,J47,J47*1000)</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="G47" s="2">
@@ -3036,7 +3105,7 @@
         <v>2</v>
       </c>
       <c r="F48" s="6">
-        <f>IF(E48=1,J48,J48*1000)</f>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="G48" s="2">
@@ -3068,7 +3137,7 @@
         <v>2</v>
       </c>
       <c r="F49" s="6">
-        <f>IF(E49=1,J49,J49*1000)</f>
+        <f t="shared" si="1"/>
         <v>60</v>
       </c>
       <c r="G49" s="2">
@@ -3100,7 +3169,7 @@
         <v>2</v>
       </c>
       <c r="F50" s="6">
-        <f>IF(E50=1,J50,J50*1000)</f>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="G50" s="2">
@@ -3132,7 +3201,7 @@
         <v>2</v>
       </c>
       <c r="F51" s="6">
-        <f>IF(E51=1,J51,J51*1000)</f>
+        <f t="shared" si="1"/>
         <v>200</v>
       </c>
       <c r="G51" s="2">
@@ -3164,7 +3233,7 @@
         <v>2</v>
       </c>
       <c r="F52" s="6">
-        <f>IF(E52=1,J52,J52*1000)</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="G52" s="2">
@@ -3196,7 +3265,7 @@
         <v>2</v>
       </c>
       <c r="F53" s="6">
-        <f>IF(E53=1,J53,J53*1000)</f>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="G53" s="2">
@@ -3228,7 +3297,7 @@
         <v>2</v>
       </c>
       <c r="F54" s="6">
-        <f>IF(E54=1,J54,J54*1000)</f>
+        <f t="shared" si="1"/>
         <v>60</v>
       </c>
       <c r="G54" s="2">
@@ -3260,7 +3329,7 @@
         <v>2</v>
       </c>
       <c r="F55" s="6">
-        <f>IF(E55=1,J55,J55*1000)</f>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="G55" s="2">
@@ -3292,7 +3361,7 @@
         <v>2</v>
       </c>
       <c r="F56" s="6">
-        <f>IF(E56=1,J56,J56*1000)</f>
+        <f t="shared" si="1"/>
         <v>200</v>
       </c>
       <c r="G56" s="2">
@@ -3324,7 +3393,7 @@
         <v>2</v>
       </c>
       <c r="F57" s="6">
-        <f>IF(E57=1,J57,J57*1000)</f>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="G57" s="2">
@@ -3356,7 +3425,7 @@
         <v>2</v>
       </c>
       <c r="F58" s="6">
-        <f>IF(E58=1,J58,J58*1000)</f>
+        <f t="shared" si="1"/>
         <v>40</v>
       </c>
       <c r="G58" s="2">
@@ -3388,7 +3457,7 @@
         <v>2</v>
       </c>
       <c r="F59" s="6">
-        <f>IF(E59=1,J59,J59*1000)</f>
+        <f t="shared" si="1"/>
         <v>120</v>
       </c>
       <c r="G59" s="2">
@@ -3420,7 +3489,7 @@
         <v>2</v>
       </c>
       <c r="F60" s="6">
-        <f>IF(E60=1,J60,J60*1000)</f>
+        <f t="shared" si="1"/>
         <v>200</v>
       </c>
       <c r="G60" s="2">
@@ -3452,7 +3521,7 @@
         <v>2</v>
       </c>
       <c r="F61" s="6">
-        <f>IF(E61=1,J61,J61*1000)</f>
+        <f t="shared" si="1"/>
         <v>400</v>
       </c>
       <c r="G61" s="2">
@@ -3484,7 +3553,7 @@
         <v>2</v>
       </c>
       <c r="F62" s="6">
-        <f>IF(E62=1,J62,J62*1000)</f>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="G62" s="2">
@@ -3516,7 +3585,7 @@
         <v>2</v>
       </c>
       <c r="F63" s="6">
-        <f>IF(E63=1,J63,J63*1000)</f>
+        <f t="shared" si="1"/>
         <v>40</v>
       </c>
       <c r="G63" s="2">
@@ -3548,7 +3617,7 @@
         <v>2</v>
       </c>
       <c r="F64" s="6">
-        <f>IF(E64=1,J64,J64*1000)</f>
+        <f t="shared" si="1"/>
         <v>120</v>
       </c>
       <c r="G64" s="2">
@@ -3580,7 +3649,7 @@
         <v>2</v>
       </c>
       <c r="F65" s="6">
-        <f>IF(E65=1,J65,J65*1000)</f>
+        <f t="shared" si="1"/>
         <v>200</v>
       </c>
       <c r="G65" s="2">
@@ -3612,7 +3681,7 @@
         <v>2</v>
       </c>
       <c r="F66" s="6">
-        <f>IF(E66=1,J66,J66*1000)</f>
+        <f t="shared" ref="F66:F97" si="2">IF(E66=1,J66,J66*1000)</f>
         <v>400</v>
       </c>
       <c r="G66" s="2">
@@ -3644,7 +3713,7 @@
         <v>2</v>
       </c>
       <c r="F67" s="6">
-        <f>IF(E67=1,J67,J67*1000)</f>
+        <f t="shared" si="2"/>
         <v>50</v>
       </c>
       <c r="G67" s="2">
@@ -3676,7 +3745,7 @@
         <v>2</v>
       </c>
       <c r="F68" s="6">
-        <f>IF(E68=1,J68,J68*1000)</f>
+        <f t="shared" si="2"/>
         <v>60</v>
       </c>
       <c r="G68" s="2">
@@ -3708,7 +3777,7 @@
         <v>2</v>
       </c>
       <c r="F69" s="6">
-        <f>IF(E69=1,J69,J69*1000)</f>
+        <f t="shared" si="2"/>
         <v>70</v>
       </c>
       <c r="G69" s="2">
@@ -3740,7 +3809,7 @@
         <v>2</v>
       </c>
       <c r="F70" s="6">
-        <f>IF(E70=1,J70,J70*1000)</f>
+        <f t="shared" si="2"/>
         <v>80</v>
       </c>
       <c r="G70" s="2">
@@ -3772,7 +3841,7 @@
         <v>2</v>
       </c>
       <c r="F71" s="6">
-        <f>IF(E71=1,J71,J71*1000)</f>
+        <f t="shared" si="2"/>
         <v>90</v>
       </c>
       <c r="G71" s="2">
@@ -3804,7 +3873,7 @@
         <v>1</v>
       </c>
       <c r="F72" s="6" t="str">
-        <f>IF(E72=1,J72,J72*1000)</f>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="G72" s="2">
@@ -3836,7 +3905,7 @@
         <v>1</v>
       </c>
       <c r="F73" s="6" t="str">
-        <f>IF(E73=1,J73,J73*1000)</f>
+        <f t="shared" si="2"/>
         <v>50</v>
       </c>
       <c r="G73" s="2">
@@ -3868,7 +3937,7 @@
         <v>1</v>
       </c>
       <c r="F74" s="6" t="str">
-        <f>IF(E74=1,J74,J74*1000)</f>
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
       <c r="G74" s="2">
@@ -3900,7 +3969,7 @@
         <v>1</v>
       </c>
       <c r="F75" s="6" t="str">
-        <f>IF(E75=1,J75,J75*1000)</f>
+        <f t="shared" si="2"/>
         <v>150</v>
       </c>
       <c r="G75" s="2">
@@ -3932,7 +4001,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="6" t="str">
-        <f>IF(E76=1,J76,J76*1000)</f>
+        <f t="shared" si="2"/>
         <v>250</v>
       </c>
       <c r="G76" s="2">
@@ -3964,7 +4033,7 @@
         <v>1</v>
       </c>
       <c r="F77" s="6" t="str">
-        <f>IF(E77=1,J77,J77*1000)</f>
+        <f t="shared" si="2"/>
         <v>25</v>
       </c>
       <c r="G77" s="2">
@@ -3996,7 +4065,7 @@
         <v>1</v>
       </c>
       <c r="F78" s="6" t="str">
-        <f>IF(E78=1,J78,J78*1000)</f>
+        <f t="shared" si="2"/>
         <v>50</v>
       </c>
       <c r="G78" s="2">
@@ -4028,7 +4097,7 @@
         <v>1</v>
       </c>
       <c r="F79" s="6" t="str">
-        <f>IF(E79=1,J79,J79*1000)</f>
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
       <c r="G79" s="2">
@@ -4060,7 +4129,7 @@
         <v>1</v>
       </c>
       <c r="F80" s="6" t="str">
-        <f>IF(E80=1,J80,J80*1000)</f>
+        <f t="shared" si="2"/>
         <v>150</v>
       </c>
       <c r="G80" s="2">
@@ -4092,7 +4161,7 @@
         <v>1</v>
       </c>
       <c r="F81" s="6" t="str">
-        <f>IF(E81=1,J81,J81*1000)</f>
+        <f t="shared" si="2"/>
         <v>250</v>
       </c>
       <c r="G81" s="2">
@@ -4124,7 +4193,7 @@
         <v>2</v>
       </c>
       <c r="F82" s="6">
-        <f>IF(E82=1,J82,J82*1000)</f>
+        <f t="shared" si="2"/>
         <v>30</v>
       </c>
       <c r="G82" s="2">
@@ -4156,7 +4225,7 @@
         <v>2</v>
       </c>
       <c r="F83" s="6">
-        <f>IF(E83=1,J83,J83*1000)</f>
+        <f t="shared" si="2"/>
         <v>35</v>
       </c>
       <c r="G83" s="2">
@@ -4188,7 +4257,7 @@
         <v>2</v>
       </c>
       <c r="F84" s="6">
-        <f>IF(E84=1,J84,J84*1000)</f>
+        <f t="shared" si="2"/>
         <v>40</v>
       </c>
       <c r="G84" s="2">
@@ -4220,7 +4289,7 @@
         <v>2</v>
       </c>
       <c r="F85" s="6">
-        <f>IF(E85=1,J85,J85*1000)</f>
+        <f t="shared" si="2"/>
         <v>45</v>
       </c>
       <c r="G85" s="2">
@@ -4252,7 +4321,7 @@
         <v>2</v>
       </c>
       <c r="F86" s="6">
-        <f>IF(E86=1,J86,J86*1000)</f>
+        <f t="shared" si="2"/>
         <v>50</v>
       </c>
       <c r="G86" s="2">
@@ -5396,4 +5465,2389 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AC063B5-2DDF-41F0-8C7C-824BAB815EE4}">
+  <dimension ref="A1:I85"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2">
+        <f>VLOOKUP(H2,Sheet1!B:F,5,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="6">
+        <f>IF(D2=1,I2,I2*1000)</f>
+        <v>0</v>
+      </c>
+      <c r="F2" s="2">
+        <v>1</v>
+      </c>
+      <c r="H2" s="2">
+        <v>16384</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2">
+        <f>VLOOKUP(H3,Sheet1!B:F,5,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1</v>
+      </c>
+      <c r="E3" s="6" t="str">
+        <f t="shared" ref="E3:E66" si="0">IF(D3=1,I3,I3*1000)</f>
+        <v>1400</v>
+      </c>
+      <c r="F3" s="2">
+        <v>12</v>
+      </c>
+      <c r="H3" s="2">
+        <v>4097</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2">
+        <v>2</v>
+      </c>
+      <c r="C4" s="2">
+        <f>VLOOKUP(H4,Sheet1!B:F,5,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1</v>
+      </c>
+      <c r="E4" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>1500</v>
+      </c>
+      <c r="F4" s="2">
+        <v>13</v>
+      </c>
+      <c r="H4" s="2">
+        <v>4097</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2">
+        <v>2</v>
+      </c>
+      <c r="C5" s="2">
+        <f>VLOOKUP(H5,Sheet1!B:F,5,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1</v>
+      </c>
+      <c r="E5" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>2000</v>
+      </c>
+      <c r="F5" s="2">
+        <v>14</v>
+      </c>
+      <c r="H5" s="2">
+        <v>4097</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2">
+        <v>2</v>
+      </c>
+      <c r="C6" s="2">
+        <f>VLOOKUP(H6,Sheet1!B:F,5,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+      <c r="E6" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="F6" s="2">
+        <v>21</v>
+      </c>
+      <c r="H6" s="2">
+        <v>4098</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2">
+        <v>2</v>
+      </c>
+      <c r="C7" s="2">
+        <f>VLOOKUP(H7,Sheet1!B:F,5,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1</v>
+      </c>
+      <c r="E7" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+      <c r="F7" s="2">
+        <v>22</v>
+      </c>
+      <c r="H7" s="2">
+        <v>4098</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2">
+        <v>2</v>
+      </c>
+      <c r="C8" s="2">
+        <f>VLOOKUP(H8,Sheet1!B:F,5,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1</v>
+      </c>
+      <c r="E8" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+      <c r="F8" s="2">
+        <v>23</v>
+      </c>
+      <c r="H8" s="2">
+        <v>4098</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2">
+        <v>2</v>
+      </c>
+      <c r="C9" s="2">
+        <f>VLOOKUP(H9,Sheet1!B:F,5,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1</v>
+      </c>
+      <c r="E9" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F9" s="2">
+        <v>24</v>
+      </c>
+      <c r="H9" s="2">
+        <v>4098</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2">
+        <v>2</v>
+      </c>
+      <c r="C10" s="2">
+        <f>VLOOKUP(H10,Sheet1!B:F,5,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1</v>
+      </c>
+      <c r="E10" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>120</v>
+      </c>
+      <c r="F10" s="2">
+        <v>25</v>
+      </c>
+      <c r="H10" s="2">
+        <v>4098</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2">
+        <v>2</v>
+      </c>
+      <c r="C11" s="2">
+        <f>VLOOKUP(H11,Sheet1!B:F,5,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1</v>
+      </c>
+      <c r="E11" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>150</v>
+      </c>
+      <c r="F11" s="2">
+        <v>26</v>
+      </c>
+      <c r="H11" s="2">
+        <v>4098</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2">
+        <v>2</v>
+      </c>
+      <c r="C12" s="2">
+        <f>VLOOKUP(H12,Sheet1!B:F,5,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D12" s="2">
+        <v>1</v>
+      </c>
+      <c r="E12" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="F12" s="2">
+        <v>27</v>
+      </c>
+      <c r="H12" s="2">
+        <v>4098</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2">
+        <v>2</v>
+      </c>
+      <c r="C13" s="2">
+        <f>VLOOKUP(H13,Sheet1!B:F,5,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="D13" s="2">
+        <v>1</v>
+      </c>
+      <c r="E13" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="F13" s="2">
+        <v>31</v>
+      </c>
+      <c r="H13" s="2">
+        <v>4099</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2">
+        <v>2</v>
+      </c>
+      <c r="C14" s="2">
+        <f>VLOOKUP(H14,Sheet1!B:F,5,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="D14" s="2">
+        <v>1</v>
+      </c>
+      <c r="E14" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+      <c r="F14" s="2">
+        <v>32</v>
+      </c>
+      <c r="H14" s="2">
+        <v>4099</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2">
+        <v>2</v>
+      </c>
+      <c r="C15" s="2">
+        <f>VLOOKUP(H15,Sheet1!B:F,5,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="D15" s="2">
+        <v>1</v>
+      </c>
+      <c r="E15" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+      <c r="F15" s="2">
+        <v>33</v>
+      </c>
+      <c r="H15" s="2">
+        <v>4099</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2">
+        <v>2</v>
+      </c>
+      <c r="C16" s="2">
+        <f>VLOOKUP(H16,Sheet1!B:F,5,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="D16" s="2">
+        <v>1</v>
+      </c>
+      <c r="E16" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F16" s="2">
+        <v>34</v>
+      </c>
+      <c r="H16" s="2">
+        <v>4099</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2">
+        <v>2</v>
+      </c>
+      <c r="C17" s="2">
+        <f>VLOOKUP(H17,Sheet1!B:F,5,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="D17" s="2">
+        <v>1</v>
+      </c>
+      <c r="E17" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>120</v>
+      </c>
+      <c r="F17" s="2">
+        <v>35</v>
+      </c>
+      <c r="H17" s="2">
+        <v>4099</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2">
+        <v>2</v>
+      </c>
+      <c r="C18" s="2">
+        <f>VLOOKUP(H18,Sheet1!B:F,5,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="D18" s="2">
+        <v>1</v>
+      </c>
+      <c r="E18" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>150</v>
+      </c>
+      <c r="F18" s="2">
+        <v>36</v>
+      </c>
+      <c r="H18" s="2">
+        <v>4099</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2">
+        <v>2</v>
+      </c>
+      <c r="C19" s="2">
+        <f>VLOOKUP(H19,Sheet1!B:F,5,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="D19" s="2">
+        <v>1</v>
+      </c>
+      <c r="E19" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="F19" s="2">
+        <v>37</v>
+      </c>
+      <c r="H19" s="2">
+        <v>4099</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2">
+        <v>2</v>
+      </c>
+      <c r="C20" s="2">
+        <f>VLOOKUP(H20,Sheet1!B:F,5,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D20" s="2">
+        <v>1</v>
+      </c>
+      <c r="E20" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="F20" s="2">
+        <v>41</v>
+      </c>
+      <c r="H20" s="2">
+        <v>4100</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2">
+        <v>2</v>
+      </c>
+      <c r="C21" s="2">
+        <f>VLOOKUP(H21,Sheet1!B:F,5,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D21" s="2">
+        <v>1</v>
+      </c>
+      <c r="E21" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+      <c r="F21" s="2">
+        <v>42</v>
+      </c>
+      <c r="H21" s="2">
+        <v>4100</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2">
+        <v>2</v>
+      </c>
+      <c r="C22" s="2">
+        <f>VLOOKUP(H22,Sheet1!B:F,5,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D22" s="2">
+        <v>1</v>
+      </c>
+      <c r="E22" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F22" s="2">
+        <v>43</v>
+      </c>
+      <c r="H22" s="2">
+        <v>4100</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2">
+        <v>2</v>
+      </c>
+      <c r="C23" s="2">
+        <f>VLOOKUP(H23,Sheet1!B:F,5,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D23" s="2">
+        <v>1</v>
+      </c>
+      <c r="E23" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>150</v>
+      </c>
+      <c r="F23" s="2">
+        <v>44</v>
+      </c>
+      <c r="H23" s="2">
+        <v>4100</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2">
+        <v>2</v>
+      </c>
+      <c r="C24" s="2">
+        <f>VLOOKUP(H24,Sheet1!B:F,5,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="D24" s="2">
+        <v>1</v>
+      </c>
+      <c r="E24" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="F24" s="2">
+        <v>51</v>
+      </c>
+      <c r="H24" s="2">
+        <v>4101</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2">
+        <v>2</v>
+      </c>
+      <c r="C25" s="2">
+        <f>VLOOKUP(H25,Sheet1!B:F,5,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="D25" s="2">
+        <v>1</v>
+      </c>
+      <c r="E25" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+      <c r="F25" s="2">
+        <v>52</v>
+      </c>
+      <c r="H25" s="2">
+        <v>4101</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2">
+        <v>2</v>
+      </c>
+      <c r="C26" s="2">
+        <f>VLOOKUP(H26,Sheet1!B:F,5,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="D26" s="2">
+        <v>1</v>
+      </c>
+      <c r="E26" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F26" s="2">
+        <v>53</v>
+      </c>
+      <c r="H26" s="2">
+        <v>4101</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2">
+        <v>2</v>
+      </c>
+      <c r="C27" s="2">
+        <f>VLOOKUP(H27,Sheet1!B:F,5,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="D27" s="2">
+        <v>1</v>
+      </c>
+      <c r="E27" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>150</v>
+      </c>
+      <c r="F27" s="2">
+        <v>54</v>
+      </c>
+      <c r="H27" s="2">
+        <v>4101</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2">
+        <v>2</v>
+      </c>
+      <c r="C28" s="2">
+        <f>VLOOKUP(H28,Sheet1!B:F,5,FALSE)</f>
+        <v>7</v>
+      </c>
+      <c r="D28" s="2">
+        <v>1</v>
+      </c>
+      <c r="E28" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="F28" s="2">
+        <v>71</v>
+      </c>
+      <c r="H28" s="2">
+        <v>4103</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2">
+        <v>2</v>
+      </c>
+      <c r="C29" s="2">
+        <f>VLOOKUP(H29,Sheet1!B:F,5,FALSE)</f>
+        <v>7</v>
+      </c>
+      <c r="D29" s="2">
+        <v>1</v>
+      </c>
+      <c r="E29" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>75</v>
+      </c>
+      <c r="F29" s="2">
+        <v>72</v>
+      </c>
+      <c r="H29" s="2">
+        <v>4103</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2">
+        <v>2</v>
+      </c>
+      <c r="C30" s="2">
+        <f>VLOOKUP(H30,Sheet1!B:F,5,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="D30" s="2">
+        <v>1</v>
+      </c>
+      <c r="E30" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="F30" s="2">
+        <v>81</v>
+      </c>
+      <c r="H30" s="2">
+        <v>4104</v>
+      </c>
+      <c r="I30" s="7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2">
+        <v>2</v>
+      </c>
+      <c r="C31" s="2">
+        <f>VLOOKUP(H31,Sheet1!B:F,5,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="D31" s="2">
+        <v>1</v>
+      </c>
+      <c r="E31" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="F31" s="2">
+        <v>82</v>
+      </c>
+      <c r="H31" s="2">
+        <v>4104</v>
+      </c>
+      <c r="I31" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2">
+        <v>2</v>
+      </c>
+      <c r="C32" s="2">
+        <f>VLOOKUP(H32,Sheet1!B:F,5,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="D32" s="2">
+        <v>1</v>
+      </c>
+      <c r="E32" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="F32" s="2">
+        <v>83</v>
+      </c>
+      <c r="H32" s="2">
+        <v>4104</v>
+      </c>
+      <c r="I32" s="7" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2">
+        <v>2</v>
+      </c>
+      <c r="C33" s="2">
+        <f>VLOOKUP(H33,Sheet1!B:F,5,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="D33" s="2">
+        <v>1</v>
+      </c>
+      <c r="E33" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="F33" s="2">
+        <v>84</v>
+      </c>
+      <c r="H33" s="2">
+        <v>4104</v>
+      </c>
+      <c r="I33" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2">
+        <v>2</v>
+      </c>
+      <c r="C34" s="2">
+        <f>VLOOKUP(H34,Sheet1!B:F,5,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="D34" s="2">
+        <v>1</v>
+      </c>
+      <c r="E34" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="F34" s="2">
+        <v>91</v>
+      </c>
+      <c r="H34" s="2">
+        <v>4105</v>
+      </c>
+      <c r="I34" s="7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2">
+        <v>2</v>
+      </c>
+      <c r="C35" s="2">
+        <f>VLOOKUP(H35,Sheet1!B:F,5,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="D35" s="2">
+        <v>1</v>
+      </c>
+      <c r="E35" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="F35" s="2">
+        <v>92</v>
+      </c>
+      <c r="H35" s="2">
+        <v>4105</v>
+      </c>
+      <c r="I35" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2">
+        <v>2</v>
+      </c>
+      <c r="C36" s="2">
+        <f>VLOOKUP(H36,Sheet1!B:F,5,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="D36" s="2">
+        <v>1</v>
+      </c>
+      <c r="E36" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="F36" s="2">
+        <v>93</v>
+      </c>
+      <c r="H36" s="2">
+        <v>4105</v>
+      </c>
+      <c r="I36" s="7" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2">
+        <v>2</v>
+      </c>
+      <c r="C37" s="2">
+        <f>VLOOKUP(H37,Sheet1!B:F,5,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="D37" s="2">
+        <v>1</v>
+      </c>
+      <c r="E37" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="F37" s="2">
+        <v>94</v>
+      </c>
+      <c r="H37" s="2">
+        <v>4105</v>
+      </c>
+      <c r="I37" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2">
+        <v>2</v>
+      </c>
+      <c r="C38" s="2">
+        <f>VLOOKUP(H38,Sheet1!B:F,5,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="D38" s="2">
+        <v>1</v>
+      </c>
+      <c r="E38" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="F38" s="2">
+        <v>95</v>
+      </c>
+      <c r="H38" s="2">
+        <v>4105</v>
+      </c>
+      <c r="I38" s="7" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2">
+        <v>2</v>
+      </c>
+      <c r="C39" s="2">
+        <f>VLOOKUP(H39,Sheet1!B:F,5,FALSE)</f>
+        <v>10</v>
+      </c>
+      <c r="D39" s="2">
+        <v>1</v>
+      </c>
+      <c r="E39" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F39" s="2">
+        <v>101</v>
+      </c>
+      <c r="H39" s="2">
+        <v>4106</v>
+      </c>
+      <c r="I39" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2">
+        <v>2</v>
+      </c>
+      <c r="C40" s="2">
+        <f>VLOOKUP(H40,Sheet1!B:F,5,FALSE)</f>
+        <v>16</v>
+      </c>
+      <c r="D40" s="2">
+        <v>1</v>
+      </c>
+      <c r="E40" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="F40" s="2">
+        <v>111</v>
+      </c>
+      <c r="H40" s="2">
+        <v>4107</v>
+      </c>
+      <c r="I40" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2">
+        <v>3</v>
+      </c>
+      <c r="C41" s="2">
+        <f>VLOOKUP(H41,Sheet1!B:F,5,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D41" s="2">
+        <v>2</v>
+      </c>
+      <c r="E41" s="6">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="F41" s="2">
+        <v>211</v>
+      </c>
+      <c r="H41" s="2">
+        <v>16385</v>
+      </c>
+      <c r="I41" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2">
+        <v>3</v>
+      </c>
+      <c r="C42" s="2">
+        <f>VLOOKUP(H42,Sheet1!B:F,5,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D42" s="2">
+        <v>2</v>
+      </c>
+      <c r="E42" s="6">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="F42" s="2">
+        <v>212</v>
+      </c>
+      <c r="H42" s="2">
+        <v>16385</v>
+      </c>
+      <c r="I42" s="7" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" s="2">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2">
+        <v>3</v>
+      </c>
+      <c r="C43" s="2">
+        <f>VLOOKUP(H43,Sheet1!B:F,5,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D43" s="2">
+        <v>2</v>
+      </c>
+      <c r="E43" s="6">
+        <f t="shared" si="0"/>
+        <v>2000</v>
+      </c>
+      <c r="F43" s="2">
+        <v>213</v>
+      </c>
+      <c r="H43" s="2">
+        <v>16385</v>
+      </c>
+      <c r="I43" s="7" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2">
+        <v>3</v>
+      </c>
+      <c r="C44" s="2">
+        <f>VLOOKUP(H44,Sheet1!B:F,5,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D44" s="2">
+        <v>2</v>
+      </c>
+      <c r="E44" s="6">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="F44" s="2">
+        <v>221</v>
+      </c>
+      <c r="H44" s="2">
+        <v>16386</v>
+      </c>
+      <c r="I44" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" s="2">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2">
+        <v>3</v>
+      </c>
+      <c r="C45" s="2">
+        <f>VLOOKUP(H45,Sheet1!B:F,5,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D45" s="2">
+        <v>2</v>
+      </c>
+      <c r="E45" s="6">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="F45" s="2">
+        <v>222</v>
+      </c>
+      <c r="H45" s="2">
+        <v>16386</v>
+      </c>
+      <c r="I45" s="7" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" s="2">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2">
+        <v>3</v>
+      </c>
+      <c r="C46" s="2">
+        <f>VLOOKUP(H46,Sheet1!B:F,5,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D46" s="2">
+        <v>2</v>
+      </c>
+      <c r="E46" s="6">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="F46" s="2">
+        <v>223</v>
+      </c>
+      <c r="H46" s="2">
+        <v>16386</v>
+      </c>
+      <c r="I46" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" s="2">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2">
+        <v>3</v>
+      </c>
+      <c r="C47" s="2">
+        <f>VLOOKUP(H47,Sheet1!B:F,5,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D47" s="2">
+        <v>2</v>
+      </c>
+      <c r="E47" s="6">
+        <f t="shared" si="0"/>
+        <v>1000</v>
+      </c>
+      <c r="F47" s="2">
+        <v>224</v>
+      </c>
+      <c r="H47" s="2">
+        <v>16386</v>
+      </c>
+      <c r="I47" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" s="2">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2">
+        <v>3</v>
+      </c>
+      <c r="C48" s="2">
+        <f>VLOOKUP(H48,Sheet1!B:F,5,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="D48" s="2">
+        <v>2</v>
+      </c>
+      <c r="E48" s="6">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="F48" s="2">
+        <v>231</v>
+      </c>
+      <c r="H48" s="2">
+        <v>16387</v>
+      </c>
+      <c r="I48" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" s="2">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2">
+        <v>3</v>
+      </c>
+      <c r="C49" s="2">
+        <f>VLOOKUP(H49,Sheet1!B:F,5,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="D49" s="2">
+        <v>2</v>
+      </c>
+      <c r="E49" s="6">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="F49" s="2">
+        <v>232</v>
+      </c>
+      <c r="H49" s="2">
+        <v>16387</v>
+      </c>
+      <c r="I49" s="7" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" s="2">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2">
+        <v>3</v>
+      </c>
+      <c r="C50" s="2">
+        <f>VLOOKUP(H50,Sheet1!B:F,5,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="D50" s="2">
+        <v>2</v>
+      </c>
+      <c r="E50" s="6">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="F50" s="2">
+        <v>233</v>
+      </c>
+      <c r="H50" s="2">
+        <v>16387</v>
+      </c>
+      <c r="I50" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" s="2">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2">
+        <v>3</v>
+      </c>
+      <c r="C51" s="2">
+        <f>VLOOKUP(H51,Sheet1!B:F,5,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="D51" s="2">
+        <v>2</v>
+      </c>
+      <c r="E51" s="6">
+        <f t="shared" si="0"/>
+        <v>1000</v>
+      </c>
+      <c r="F51" s="2">
+        <v>234</v>
+      </c>
+      <c r="H51" s="2">
+        <v>16387</v>
+      </c>
+      <c r="I51" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" s="2">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2">
+        <v>3</v>
+      </c>
+      <c r="C52" s="2">
+        <f>VLOOKUP(H52,Sheet1!B:F,5,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D52" s="2">
+        <v>2</v>
+      </c>
+      <c r="E52" s="6">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="F52" s="2">
+        <v>241</v>
+      </c>
+      <c r="H52" s="2">
+        <v>16388</v>
+      </c>
+      <c r="I52" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" s="2">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2">
+        <v>3</v>
+      </c>
+      <c r="C53" s="2">
+        <f>VLOOKUP(H53,Sheet1!B:F,5,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D53" s="2">
+        <v>2</v>
+      </c>
+      <c r="E53" s="6">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="F53" s="2">
+        <v>242</v>
+      </c>
+      <c r="H53" s="2">
+        <v>16388</v>
+      </c>
+      <c r="I53" s="7" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" s="2">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2">
+        <v>3</v>
+      </c>
+      <c r="C54" s="2">
+        <f>VLOOKUP(H54,Sheet1!B:F,5,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D54" s="2">
+        <v>2</v>
+      </c>
+      <c r="E54" s="6">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="F54" s="2">
+        <v>243</v>
+      </c>
+      <c r="H54" s="2">
+        <v>16388</v>
+      </c>
+      <c r="I54" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" s="2">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2">
+        <v>3</v>
+      </c>
+      <c r="C55" s="2">
+        <f>VLOOKUP(H55,Sheet1!B:F,5,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D55" s="2">
+        <v>2</v>
+      </c>
+      <c r="E55" s="6">
+        <f t="shared" si="0"/>
+        <v>1000</v>
+      </c>
+      <c r="F55" s="2">
+        <v>244</v>
+      </c>
+      <c r="H55" s="2">
+        <v>16388</v>
+      </c>
+      <c r="I55" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" s="2">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2">
+        <v>3</v>
+      </c>
+      <c r="C56" s="2">
+        <f>VLOOKUP(H56,Sheet1!B:F,5,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="D56" s="2">
+        <v>2</v>
+      </c>
+      <c r="E56" s="6">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="F56" s="2">
+        <v>251</v>
+      </c>
+      <c r="H56" s="2">
+        <v>16389</v>
+      </c>
+      <c r="I56" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" s="2">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2">
+        <v>3</v>
+      </c>
+      <c r="C57" s="2">
+        <f>VLOOKUP(H57,Sheet1!B:F,5,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="D57" s="2">
+        <v>2</v>
+      </c>
+      <c r="E57" s="6">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="F57" s="2">
+        <v>252</v>
+      </c>
+      <c r="H57" s="2">
+        <v>16389</v>
+      </c>
+      <c r="I57" s="7" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" s="2">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2">
+        <v>3</v>
+      </c>
+      <c r="C58" s="2">
+        <f>VLOOKUP(H58,Sheet1!B:F,5,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="D58" s="2">
+        <v>2</v>
+      </c>
+      <c r="E58" s="6">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="F58" s="2">
+        <v>253</v>
+      </c>
+      <c r="H58" s="2">
+        <v>16389</v>
+      </c>
+      <c r="I58" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A59" s="2">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2">
+        <v>3</v>
+      </c>
+      <c r="C59" s="2">
+        <f>VLOOKUP(H59,Sheet1!B:F,5,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="D59" s="2">
+        <v>2</v>
+      </c>
+      <c r="E59" s="6">
+        <f t="shared" si="0"/>
+        <v>1000</v>
+      </c>
+      <c r="F59" s="2">
+        <v>254</v>
+      </c>
+      <c r="H59" s="2">
+        <v>16389</v>
+      </c>
+      <c r="I59" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" s="2">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2">
+        <v>3</v>
+      </c>
+      <c r="C60" s="2">
+        <f>VLOOKUP(H60,Sheet1!B:F,5,FALSE)</f>
+        <v>7</v>
+      </c>
+      <c r="D60" s="2">
+        <v>2</v>
+      </c>
+      <c r="E60" s="6">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="F60" s="2">
+        <v>271</v>
+      </c>
+      <c r="H60" s="2">
+        <v>16390</v>
+      </c>
+      <c r="I60" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" s="2">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2">
+        <v>3</v>
+      </c>
+      <c r="C61" s="2">
+        <f>VLOOKUP(H61,Sheet1!B:F,5,FALSE)</f>
+        <v>7</v>
+      </c>
+      <c r="D61" s="2">
+        <v>2</v>
+      </c>
+      <c r="E61" s="6">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+      <c r="F61" s="2">
+        <v>272</v>
+      </c>
+      <c r="H61" s="2">
+        <v>16390</v>
+      </c>
+      <c r="I61" s="7" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" s="2">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2">
+        <v>3</v>
+      </c>
+      <c r="C62" s="2">
+        <f>VLOOKUP(H62,Sheet1!B:F,5,FALSE)</f>
+        <v>7</v>
+      </c>
+      <c r="D62" s="2">
+        <v>2</v>
+      </c>
+      <c r="E62" s="6">
+        <f t="shared" si="0"/>
+        <v>1000</v>
+      </c>
+      <c r="F62" s="2">
+        <v>273</v>
+      </c>
+      <c r="H62" s="2">
+        <v>16390</v>
+      </c>
+      <c r="I62" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" s="2">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2">
+        <v>3</v>
+      </c>
+      <c r="C63" s="2">
+        <f>VLOOKUP(H63,Sheet1!B:F,5,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="D63" s="2">
+        <v>2</v>
+      </c>
+      <c r="E63" s="6">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="F63" s="2">
+        <v>281</v>
+      </c>
+      <c r="H63" s="2">
+        <v>16391</v>
+      </c>
+      <c r="I63" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A64" s="2">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2">
+        <v>3</v>
+      </c>
+      <c r="C64" s="2">
+        <f>VLOOKUP(H64,Sheet1!B:F,5,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="D64" s="2">
+        <v>2</v>
+      </c>
+      <c r="E64" s="6">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="F64" s="2">
+        <v>282</v>
+      </c>
+      <c r="H64" s="2">
+        <v>16391</v>
+      </c>
+      <c r="I64" s="7" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65" s="2">
+        <v>64</v>
+      </c>
+      <c r="B65" s="2">
+        <v>3</v>
+      </c>
+      <c r="C65" s="2">
+        <f>VLOOKUP(H65,Sheet1!B:F,5,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="D65" s="2">
+        <v>2</v>
+      </c>
+      <c r="E65" s="6">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="F65" s="2">
+        <v>283</v>
+      </c>
+      <c r="H65" s="2">
+        <v>16391</v>
+      </c>
+      <c r="I65" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A66" s="2">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2">
+        <v>3</v>
+      </c>
+      <c r="C66" s="2">
+        <f>VLOOKUP(H66,Sheet1!B:F,5,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="D66" s="2">
+        <v>2</v>
+      </c>
+      <c r="E66" s="6">
+        <f t="shared" si="0"/>
+        <v>1000</v>
+      </c>
+      <c r="F66" s="2">
+        <v>284</v>
+      </c>
+      <c r="H66" s="2">
+        <v>16391</v>
+      </c>
+      <c r="I66" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A67" s="2">
+        <v>66</v>
+      </c>
+      <c r="B67" s="2">
+        <v>3</v>
+      </c>
+      <c r="C67" s="2">
+        <f>VLOOKUP(H67,Sheet1!B:F,5,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="D67" s="2">
+        <v>2</v>
+      </c>
+      <c r="E67" s="6">
+        <f t="shared" ref="E67:E85" si="1">IF(D67=1,I67,I67*1000)</f>
+        <v>200</v>
+      </c>
+      <c r="F67" s="2">
+        <v>291</v>
+      </c>
+      <c r="H67" s="2">
+        <v>16392</v>
+      </c>
+      <c r="I67" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A68" s="2">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2">
+        <v>3</v>
+      </c>
+      <c r="C68" s="2">
+        <f>VLOOKUP(H68,Sheet1!B:F,5,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="D68" s="2">
+        <v>2</v>
+      </c>
+      <c r="E68" s="6">
+        <f t="shared" si="1"/>
+        <v>300</v>
+      </c>
+      <c r="F68" s="2">
+        <v>292</v>
+      </c>
+      <c r="H68" s="2">
+        <v>16392</v>
+      </c>
+      <c r="I68" s="7" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A69" s="2">
+        <v>68</v>
+      </c>
+      <c r="B69" s="2">
+        <v>3</v>
+      </c>
+      <c r="C69" s="2">
+        <f>VLOOKUP(H69,Sheet1!B:F,5,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="D69" s="2">
+        <v>2</v>
+      </c>
+      <c r="E69" s="6">
+        <f t="shared" si="1"/>
+        <v>400</v>
+      </c>
+      <c r="F69" s="2">
+        <v>293</v>
+      </c>
+      <c r="H69" s="2">
+        <v>16392</v>
+      </c>
+      <c r="I69" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A70" s="2">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2">
+        <v>3</v>
+      </c>
+      <c r="C70" s="2">
+        <f>VLOOKUP(H70,Sheet1!B:F,5,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="D70" s="2">
+        <v>2</v>
+      </c>
+      <c r="E70" s="6">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="F70" s="2">
+        <v>294</v>
+      </c>
+      <c r="H70" s="2">
+        <v>16392</v>
+      </c>
+      <c r="I70" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A71" s="2">
+        <v>70</v>
+      </c>
+      <c r="B71" s="2">
+        <v>3</v>
+      </c>
+      <c r="C71" s="2">
+        <f>VLOOKUP(H71,Sheet1!B:F,5,FALSE)</f>
+        <v>10</v>
+      </c>
+      <c r="D71" s="2">
+        <v>2</v>
+      </c>
+      <c r="E71" s="6">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="F71" s="2">
+        <v>301</v>
+      </c>
+      <c r="H71" s="2">
+        <v>16393</v>
+      </c>
+      <c r="I71" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A72" s="2">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2">
+        <v>3</v>
+      </c>
+      <c r="C72" s="2">
+        <f>VLOOKUP(H72,Sheet1!B:F,5,FALSE)</f>
+        <v>10</v>
+      </c>
+      <c r="D72" s="2">
+        <v>2</v>
+      </c>
+      <c r="E72" s="6">
+        <f t="shared" si="1"/>
+        <v>300</v>
+      </c>
+      <c r="F72" s="2">
+        <v>302</v>
+      </c>
+      <c r="H72" s="2">
+        <v>16393</v>
+      </c>
+      <c r="I72" s="7" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73" s="2">
+        <v>72</v>
+      </c>
+      <c r="B73" s="2">
+        <v>3</v>
+      </c>
+      <c r="C73" s="2">
+        <f>VLOOKUP(H73,Sheet1!B:F,5,FALSE)</f>
+        <v>10</v>
+      </c>
+      <c r="D73" s="2">
+        <v>2</v>
+      </c>
+      <c r="E73" s="6">
+        <f t="shared" si="1"/>
+        <v>400</v>
+      </c>
+      <c r="F73" s="2">
+        <v>303</v>
+      </c>
+      <c r="H73" s="2">
+        <v>16393</v>
+      </c>
+      <c r="I73" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74" s="2">
+        <v>73</v>
+      </c>
+      <c r="B74" s="2">
+        <v>3</v>
+      </c>
+      <c r="C74" s="2">
+        <f>VLOOKUP(H74,Sheet1!B:F,5,FALSE)</f>
+        <v>10</v>
+      </c>
+      <c r="D74" s="2">
+        <v>2</v>
+      </c>
+      <c r="E74" s="6">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="F74" s="2">
+        <v>304</v>
+      </c>
+      <c r="H74" s="2">
+        <v>16393</v>
+      </c>
+      <c r="I74" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75" s="2">
+        <v>74</v>
+      </c>
+      <c r="B75" s="2">
+        <v>3</v>
+      </c>
+      <c r="C75" s="2">
+        <f>VLOOKUP(H75,Sheet1!B:F,5,FALSE)</f>
+        <v>11</v>
+      </c>
+      <c r="D75" s="2">
+        <v>2</v>
+      </c>
+      <c r="E75" s="6">
+        <f t="shared" si="1"/>
+        <v>4000</v>
+      </c>
+      <c r="F75" s="2">
+        <v>411</v>
+      </c>
+      <c r="H75" s="2">
+        <v>16395</v>
+      </c>
+      <c r="I75" s="7" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76" s="2">
+        <v>75</v>
+      </c>
+      <c r="B76" s="2">
+        <v>3</v>
+      </c>
+      <c r="C76" s="2">
+        <f>VLOOKUP(H76,Sheet1!B:F,5,FALSE)</f>
+        <v>11</v>
+      </c>
+      <c r="D76" s="2">
+        <v>2</v>
+      </c>
+      <c r="E76" s="6">
+        <f t="shared" si="1"/>
+        <v>6500</v>
+      </c>
+      <c r="F76" s="2">
+        <v>412</v>
+      </c>
+      <c r="H76" s="2">
+        <v>16395</v>
+      </c>
+      <c r="I76" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A77" s="2">
+        <v>76</v>
+      </c>
+      <c r="B77" s="2">
+        <v>3</v>
+      </c>
+      <c r="C77" s="2">
+        <f>VLOOKUP(H77,Sheet1!B:F,5,FALSE)</f>
+        <v>11</v>
+      </c>
+      <c r="D77" s="2">
+        <v>2</v>
+      </c>
+      <c r="E77" s="6">
+        <f t="shared" si="1"/>
+        <v>9000</v>
+      </c>
+      <c r="F77" s="2">
+        <v>413</v>
+      </c>
+      <c r="H77" s="2">
+        <v>16395</v>
+      </c>
+      <c r="I77" s="7" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A78" s="2">
+        <v>77</v>
+      </c>
+      <c r="B78" s="2">
+        <v>3</v>
+      </c>
+      <c r="C78" s="2">
+        <f>VLOOKUP(H78,Sheet1!B:F,5,FALSE)</f>
+        <v>11</v>
+      </c>
+      <c r="D78" s="2">
+        <v>2</v>
+      </c>
+      <c r="E78" s="6">
+        <f t="shared" si="1"/>
+        <v>14000</v>
+      </c>
+      <c r="F78" s="2">
+        <v>414</v>
+      </c>
+      <c r="H78" s="2">
+        <v>16395</v>
+      </c>
+      <c r="I78" s="7" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A79" s="2">
+        <v>78</v>
+      </c>
+      <c r="B79" s="2">
+        <v>3</v>
+      </c>
+      <c r="C79" s="2">
+        <f>VLOOKUP(H79,Sheet1!B:F,5,FALSE)</f>
+        <v>12</v>
+      </c>
+      <c r="D79" s="2">
+        <v>2</v>
+      </c>
+      <c r="E79" s="6">
+        <f t="shared" si="1"/>
+        <v>4000</v>
+      </c>
+      <c r="F79" s="2">
+        <v>421</v>
+      </c>
+      <c r="H79" s="2">
+        <v>16396</v>
+      </c>
+      <c r="I79" s="7" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A80" s="2">
+        <v>79</v>
+      </c>
+      <c r="B80" s="2">
+        <v>3</v>
+      </c>
+      <c r="C80" s="2">
+        <f>VLOOKUP(H80,Sheet1!B:F,5,FALSE)</f>
+        <v>12</v>
+      </c>
+      <c r="D80" s="2">
+        <v>2</v>
+      </c>
+      <c r="E80" s="6">
+        <f t="shared" si="1"/>
+        <v>6500</v>
+      </c>
+      <c r="F80" s="2">
+        <v>422</v>
+      </c>
+      <c r="H80" s="2">
+        <v>16396</v>
+      </c>
+      <c r="I80" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A81" s="2">
+        <v>80</v>
+      </c>
+      <c r="B81" s="2">
+        <v>3</v>
+      </c>
+      <c r="C81" s="2">
+        <f>VLOOKUP(H81,Sheet1!B:F,5,FALSE)</f>
+        <v>12</v>
+      </c>
+      <c r="D81" s="2">
+        <v>2</v>
+      </c>
+      <c r="E81" s="6">
+        <f t="shared" si="1"/>
+        <v>9000</v>
+      </c>
+      <c r="F81" s="2">
+        <v>423</v>
+      </c>
+      <c r="H81" s="2">
+        <v>16396</v>
+      </c>
+      <c r="I81" s="7" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A82" s="2">
+        <v>81</v>
+      </c>
+      <c r="B82" s="2">
+        <v>3</v>
+      </c>
+      <c r="C82" s="2">
+        <f>VLOOKUP(H82,Sheet1!B:F,5,FALSE)</f>
+        <v>12</v>
+      </c>
+      <c r="D82" s="2">
+        <v>2</v>
+      </c>
+      <c r="E82" s="6">
+        <f t="shared" si="1"/>
+        <v>14000</v>
+      </c>
+      <c r="F82" s="2">
+        <v>424</v>
+      </c>
+      <c r="H82" s="2">
+        <v>16396</v>
+      </c>
+      <c r="I82" s="7" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A83" s="2">
+        <v>82</v>
+      </c>
+      <c r="B83" s="2">
+        <v>3</v>
+      </c>
+      <c r="C83" s="2">
+        <f>VLOOKUP(H83,Sheet1!B:F,5,FALSE)</f>
+        <v>13</v>
+      </c>
+      <c r="D83" s="2">
+        <v>1</v>
+      </c>
+      <c r="E83" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="F83" s="2">
+        <v>431</v>
+      </c>
+      <c r="H83" s="2">
+        <v>16397</v>
+      </c>
+      <c r="I83" s="7" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A84" s="2">
+        <v>83</v>
+      </c>
+      <c r="B84" s="2">
+        <v>2</v>
+      </c>
+      <c r="C84" s="2">
+        <f>VLOOKUP(H84,Sheet1!B:F,5,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D84" s="2">
+        <v>1</v>
+      </c>
+      <c r="E84" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>3000</v>
+      </c>
+      <c r="F84" s="2">
+        <v>15</v>
+      </c>
+      <c r="H84" s="2">
+        <v>4097</v>
+      </c>
+      <c r="I84" s="7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A85" s="2">
+        <v>84</v>
+      </c>
+      <c r="B85" s="2">
+        <v>2</v>
+      </c>
+      <c r="C85" s="2">
+        <f>VLOOKUP(H85,Sheet1!B:F,5,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D85" s="2">
+        <v>1</v>
+      </c>
+      <c r="E85" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>1200</v>
+      </c>
+      <c r="F85" s="2">
+        <v>11</v>
+      </c>
+      <c r="H85" s="2">
+        <v>4097</v>
+      </c>
+      <c r="I85" s="7" t="s">
+        <v>122</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Database/Table/Boost.xlsx
+++ b/Database/Table/Boost.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyProjects\Ju.GundamWars\Database\Table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09C90C36-C4BD-4535-AD27-045B508B88E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AC152D0-8C34-4418-B84F-D5015B46FED0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14370" yWindow="0" windowWidth="14430" windowHeight="15600" tabRatio="677" activeTab="3" xr2:uid="{2B7B1DB3-ED5C-41A5-9C29-22C9C7198DDD}"/>
+    <workbookView xWindow="8475" yWindow="795" windowWidth="16770" windowHeight="13965" tabRatio="677" activeTab="3" xr2:uid="{2B7B1DB3-ED5C-41A5-9C29-22C9C7198DDD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="126">
   <si>
     <t>機体</t>
   </si>
@@ -413,6 +413,15 @@
   </si>
   <si>
     <t>1200</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>4000</t>
+  </si>
+  <si>
+    <t>2500</t>
   </si>
 </sst>
 </file>
@@ -442,7 +451,7 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -452,6 +461,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF87E7AD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -485,7 +500,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -509,6 +524,9 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3681,7 +3699,7 @@
         <v>2</v>
       </c>
       <c r="F66" s="6">
-        <f t="shared" ref="F66:F97" si="2">IF(E66=1,J66,J66*1000)</f>
+        <f t="shared" ref="F66:F86" si="2">IF(E66=1,J66,J66*1000)</f>
         <v>400</v>
       </c>
       <c r="G66" s="2">
@@ -4342,7 +4360,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EDF7545-3DBA-4B7B-9D6E-0A8559E842B2}">
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -4352,11 +4370,11 @@
       <c r="B1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="1"/>
+      <c r="C1" s="8"/>
       <c r="D1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="8" t="s">
         <v>64</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -4412,7 +4430,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="6" t="str">
-        <f t="shared" ref="E3:E40" si="0">IF(D3=1,I3,I3*1000)</f>
+        <f t="shared" ref="E3:E45" si="0">IF(D3=1,I3,I3*1000)</f>
         <v>1500</v>
       </c>
       <c r="F3" s="2">
@@ -5312,7 +5330,7 @@
         <v>20</v>
       </c>
       <c r="F35" s="2">
-        <v>111</v>
+        <v>181</v>
       </c>
       <c r="H35" s="2">
         <v>4110</v>
@@ -5340,7 +5358,7 @@
         <v>30</v>
       </c>
       <c r="F36" s="2">
-        <v>112</v>
+        <v>182</v>
       </c>
       <c r="H36" s="2">
         <v>4110</v>
@@ -5368,7 +5386,7 @@
         <v>20</v>
       </c>
       <c r="F37" s="2">
-        <v>121</v>
+        <v>191</v>
       </c>
       <c r="H37" s="2">
         <v>4111</v>
@@ -5396,7 +5414,7 @@
         <v>30</v>
       </c>
       <c r="F38" s="2">
-        <v>122</v>
+        <v>192</v>
       </c>
       <c r="H38" s="2">
         <v>4111</v>
@@ -5424,7 +5442,7 @@
         <v>20</v>
       </c>
       <c r="F39" s="2">
-        <v>131</v>
+        <v>201</v>
       </c>
       <c r="H39" s="2">
         <v>4112</v>
@@ -5452,13 +5470,153 @@
         <v>50</v>
       </c>
       <c r="F40" s="2">
-        <v>132</v>
+        <v>202</v>
       </c>
       <c r="H40" s="2">
         <v>4112</v>
       </c>
       <c r="I40" s="7" t="s">
         <v>85</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2">
+        <v>4</v>
+      </c>
+      <c r="C41" s="2">
+        <f>VLOOKUP(H41,Sheet1!B:F,5,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="D41" s="2">
+        <v>1</v>
+      </c>
+      <c r="E41" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>75</v>
+      </c>
+      <c r="F41" s="2">
+        <v>94</v>
+      </c>
+      <c r="H41" s="2">
+        <v>4105</v>
+      </c>
+      <c r="I41" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2">
+        <v>4</v>
+      </c>
+      <c r="C42" s="2">
+        <f>VLOOKUP(H42,Sheet1!B:F,5,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="D42" s="2">
+        <v>1</v>
+      </c>
+      <c r="E42" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>150</v>
+      </c>
+      <c r="F42" s="2">
+        <v>84</v>
+      </c>
+      <c r="H42" s="2">
+        <v>4104</v>
+      </c>
+      <c r="I42" s="7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" s="2">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2">
+        <v>4</v>
+      </c>
+      <c r="C43" s="2">
+        <f>VLOOKUP(H43,Sheet1!B:F,5,FALSE)</f>
+        <v>10</v>
+      </c>
+      <c r="D43" s="2">
+        <v>1</v>
+      </c>
+      <c r="E43" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="F43" s="2">
+        <v>104</v>
+      </c>
+      <c r="H43" s="2">
+        <v>4106</v>
+      </c>
+      <c r="I43" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2">
+        <v>3</v>
+      </c>
+      <c r="C44" s="2">
+        <f>VLOOKUP(H44,Sheet1!B:F,5,FALSE)</f>
+        <v>12</v>
+      </c>
+      <c r="D44" s="2">
+        <v>2</v>
+      </c>
+      <c r="E44" s="6">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="F44" s="2">
+        <v>193</v>
+      </c>
+      <c r="H44" s="2">
+        <v>4111</v>
+      </c>
+      <c r="I44" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" s="2">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2">
+        <v>3</v>
+      </c>
+      <c r="C45" s="2">
+        <f>VLOOKUP(H45,Sheet1!B:F,5,FALSE)</f>
+        <v>11</v>
+      </c>
+      <c r="D45" s="2">
+        <v>2</v>
+      </c>
+      <c r="E45" s="6">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="F45" s="2">
+        <v>183</v>
+      </c>
+      <c r="H45" s="2">
+        <v>4110</v>
+      </c>
+      <c r="I45" s="7" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -5469,7 +5627,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AC063B5-2DDF-41F0-8C7C-824BAB815EE4}">
-  <dimension ref="A1:I85"/>
+  <dimension ref="A1:I101"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -5479,11 +5637,11 @@
       <c r="B1" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C1" s="1"/>
+      <c r="C1" s="8"/>
       <c r="D1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E1" s="1"/>
+      <c r="E1" s="8"/>
       <c r="F1" s="1" t="s">
         <v>65</v>
       </c>
@@ -5541,7 +5699,7 @@
         <v>1400</v>
       </c>
       <c r="F3" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H3" s="2">
         <v>4097</v>
@@ -5569,7 +5727,7 @@
         <v>1500</v>
       </c>
       <c r="F4" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H4" s="2">
         <v>4097</v>
@@ -5597,7 +5755,7 @@
         <v>2000</v>
       </c>
       <c r="F5" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H5" s="2">
         <v>4097</v>
@@ -5625,7 +5783,7 @@
         <v>60</v>
       </c>
       <c r="F6" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H6" s="2">
         <v>4098</v>
@@ -5653,7 +5811,7 @@
         <v>70</v>
       </c>
       <c r="F7" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H7" s="2">
         <v>4098</v>
@@ -5681,7 +5839,7 @@
         <v>90</v>
       </c>
       <c r="F8" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H8" s="2">
         <v>4098</v>
@@ -5709,7 +5867,7 @@
         <v>100</v>
       </c>
       <c r="F9" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H9" s="2">
         <v>4098</v>
@@ -5737,7 +5895,7 @@
         <v>120</v>
       </c>
       <c r="F10" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H10" s="2">
         <v>4098</v>
@@ -5765,7 +5923,7 @@
         <v>150</v>
       </c>
       <c r="F11" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H11" s="2">
         <v>4098</v>
@@ -5793,7 +5951,7 @@
         <v>200</v>
       </c>
       <c r="F12" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H12" s="2">
         <v>4098</v>
@@ -5821,7 +5979,7 @@
         <v>60</v>
       </c>
       <c r="F13" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H13" s="2">
         <v>4099</v>
@@ -5849,7 +6007,7 @@
         <v>70</v>
       </c>
       <c r="F14" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H14" s="2">
         <v>4099</v>
@@ -5877,7 +6035,7 @@
         <v>90</v>
       </c>
       <c r="F15" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H15" s="2">
         <v>4099</v>
@@ -5905,7 +6063,7 @@
         <v>100</v>
       </c>
       <c r="F16" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H16" s="2">
         <v>4099</v>
@@ -5933,7 +6091,7 @@
         <v>120</v>
       </c>
       <c r="F17" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H17" s="2">
         <v>4099</v>
@@ -5961,7 +6119,7 @@
         <v>150</v>
       </c>
       <c r="F18" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H18" s="2">
         <v>4099</v>
@@ -5989,7 +6147,7 @@
         <v>200</v>
       </c>
       <c r="F19" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H19" s="2">
         <v>4099</v>
@@ -6521,7 +6679,7 @@
         <v>80</v>
       </c>
       <c r="F38" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H38" s="2">
         <v>4105</v>
@@ -6549,7 +6707,7 @@
         <v>100</v>
       </c>
       <c r="F39" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H39" s="2">
         <v>4106</v>
@@ -6661,7 +6819,7 @@
         <v>2000</v>
       </c>
       <c r="F43" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H43" s="2">
         <v>16385</v>
@@ -7329,7 +7487,7 @@
         <v>2</v>
       </c>
       <c r="E67" s="6">
-        <f t="shared" ref="E67:E85" si="1">IF(D67=1,I67,I67*1000)</f>
+        <f t="shared" ref="E67:E101" si="1">IF(D67=1,I67,I67*1000)</f>
         <v>200</v>
       </c>
       <c r="F67" s="2">
@@ -7809,7 +7967,7 @@
         <v>3000</v>
       </c>
       <c r="F84" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H84" s="2">
         <v>4097</v>
@@ -7837,13 +7995,461 @@
         <v>1200</v>
       </c>
       <c r="F85" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H85" s="2">
         <v>4097</v>
       </c>
       <c r="I85" s="7" t="s">
         <v>122</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A86" s="2">
+        <v>85</v>
+      </c>
+      <c r="B86" s="2">
+        <v>2</v>
+      </c>
+      <c r="C86" s="2">
+        <f>VLOOKUP(H86,Sheet1!B:F,5,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D86" s="2">
+        <v>1</v>
+      </c>
+      <c r="E86" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="F86" s="2">
+        <v>11</v>
+      </c>
+      <c r="H86" s="2">
+        <v>4097</v>
+      </c>
+      <c r="I86" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A87" s="2">
+        <v>86</v>
+      </c>
+      <c r="B87" s="2">
+        <v>2</v>
+      </c>
+      <c r="C87" s="2">
+        <f>VLOOKUP(H87,Sheet1!B:F,5,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="D87" s="2">
+        <v>1</v>
+      </c>
+      <c r="E87" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="F87" s="2">
+        <v>86</v>
+      </c>
+      <c r="H87" s="2">
+        <v>4104</v>
+      </c>
+      <c r="I87" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A88" s="2">
+        <v>87</v>
+      </c>
+      <c r="B88" s="2">
+        <v>2</v>
+      </c>
+      <c r="C88" s="2">
+        <f>VLOOKUP(H88,Sheet1!B:F,5,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D88" s="2">
+        <v>1</v>
+      </c>
+      <c r="E88" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>4000</v>
+      </c>
+      <c r="F88" s="2">
+        <v>18</v>
+      </c>
+      <c r="H88" s="2">
+        <v>4097</v>
+      </c>
+      <c r="I88" s="7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A89" s="2">
+        <v>88</v>
+      </c>
+      <c r="B89" s="2">
+        <v>2</v>
+      </c>
+      <c r="C89" s="2">
+        <f>VLOOKUP(H89,Sheet1!B:F,5,FALSE)</f>
+        <v>7</v>
+      </c>
+      <c r="D89" s="2">
+        <v>1</v>
+      </c>
+      <c r="E89" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="F89" s="2">
+        <v>73</v>
+      </c>
+      <c r="H89" s="2">
+        <v>4103</v>
+      </c>
+      <c r="I89" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A90" s="2">
+        <v>89</v>
+      </c>
+      <c r="B90" s="2">
+        <v>2</v>
+      </c>
+      <c r="C90" s="2">
+        <f>VLOOKUP(H90,Sheet1!B:F,5,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="D90" s="2">
+        <v>1</v>
+      </c>
+      <c r="E90" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>70</v>
+      </c>
+      <c r="F90" s="2">
+        <v>85</v>
+      </c>
+      <c r="H90" s="2">
+        <v>4104</v>
+      </c>
+      <c r="I90" s="7" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A91" s="2">
+        <v>90</v>
+      </c>
+      <c r="B91" s="2">
+        <v>2</v>
+      </c>
+      <c r="C91" s="2">
+        <f>VLOOKUP(H91,Sheet1!B:F,5,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="D91" s="2">
+        <v>1</v>
+      </c>
+      <c r="E91" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="F91" s="2">
+        <v>97</v>
+      </c>
+      <c r="H91" s="2">
+        <v>4105</v>
+      </c>
+      <c r="I91" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A92" s="2">
+        <v>91</v>
+      </c>
+      <c r="B92" s="2">
+        <v>2</v>
+      </c>
+      <c r="C92" s="2">
+        <f>VLOOKUP(H92,Sheet1!B:F,5,FALSE)</f>
+        <v>10</v>
+      </c>
+      <c r="D92" s="2">
+        <v>1</v>
+      </c>
+      <c r="E92" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="F92" s="2">
+        <v>101</v>
+      </c>
+      <c r="H92" s="2">
+        <v>4106</v>
+      </c>
+      <c r="I92" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A93" s="2">
+        <v>92</v>
+      </c>
+      <c r="B93" s="2">
+        <v>2</v>
+      </c>
+      <c r="C93" s="2">
+        <f>VLOOKUP(H93,Sheet1!B:F,5,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="D93" s="2">
+        <v>1</v>
+      </c>
+      <c r="E93" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="F93" s="2">
+        <v>31</v>
+      </c>
+      <c r="H93" s="2">
+        <v>4099</v>
+      </c>
+      <c r="I93" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A94" s="2">
+        <v>93</v>
+      </c>
+      <c r="B94" s="2">
+        <v>2</v>
+      </c>
+      <c r="C94" s="2">
+        <f>VLOOKUP(H94,Sheet1!B:F,5,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D94" s="2">
+        <v>1</v>
+      </c>
+      <c r="E94" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="F94" s="2">
+        <v>21</v>
+      </c>
+      <c r="H94" s="2">
+        <v>4098</v>
+      </c>
+      <c r="I94" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A95" s="2">
+        <v>94</v>
+      </c>
+      <c r="B95" s="2">
+        <v>2</v>
+      </c>
+      <c r="C95" s="2">
+        <f>VLOOKUP(H95,Sheet1!B:F,5,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="D95" s="2">
+        <v>1</v>
+      </c>
+      <c r="E95" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>70</v>
+      </c>
+      <c r="F95" s="2">
+        <v>95</v>
+      </c>
+      <c r="H95" s="2">
+        <v>4105</v>
+      </c>
+      <c r="I95" s="7" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A96" s="2">
+        <v>95</v>
+      </c>
+      <c r="B96" s="2">
+        <v>3</v>
+      </c>
+      <c r="C96" s="2">
+        <f>VLOOKUP(H96,Sheet1!B:F,5,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D96" s="2">
+        <v>2</v>
+      </c>
+      <c r="E96" s="6">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="F96" s="2">
+        <v>213</v>
+      </c>
+      <c r="H96" s="2">
+        <v>16385</v>
+      </c>
+      <c r="I96" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A97" s="2">
+        <v>96</v>
+      </c>
+      <c r="B97" s="2">
+        <v>2</v>
+      </c>
+      <c r="C97" s="2">
+        <f>VLOOKUP(H97,Sheet1!B:F,5,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D97" s="2">
+        <v>1</v>
+      </c>
+      <c r="E97" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>2500</v>
+      </c>
+      <c r="F97" s="2">
+        <v>16</v>
+      </c>
+      <c r="H97" s="2">
+        <v>4097</v>
+      </c>
+      <c r="I97" s="7" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A98" s="2">
+        <v>97</v>
+      </c>
+      <c r="B98" s="2">
+        <v>2</v>
+      </c>
+      <c r="C98" s="2">
+        <f>VLOOKUP(H98,Sheet1!B:F,5,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="D98" s="2">
+        <v>1</v>
+      </c>
+      <c r="E98" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>300</v>
+      </c>
+      <c r="F98" s="2">
+        <v>39</v>
+      </c>
+      <c r="H98" s="2">
+        <v>4099</v>
+      </c>
+      <c r="I98" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A99" s="2">
+        <v>98</v>
+      </c>
+      <c r="B99" s="2">
+        <v>2</v>
+      </c>
+      <c r="C99" s="2">
+        <f>VLOOKUP(H99,Sheet1!B:F,5,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D99" s="2">
+        <v>1</v>
+      </c>
+      <c r="E99" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>300</v>
+      </c>
+      <c r="F99" s="2">
+        <v>29</v>
+      </c>
+      <c r="H99" s="2">
+        <v>4098</v>
+      </c>
+      <c r="I99" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A100" s="2">
+        <v>99</v>
+      </c>
+      <c r="B100" s="2">
+        <v>2</v>
+      </c>
+      <c r="C100" s="2">
+        <f>VLOOKUP(H100,Sheet1!B:F,5,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D100" s="2">
+        <v>1</v>
+      </c>
+      <c r="E100" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="F100" s="2">
+        <v>45</v>
+      </c>
+      <c r="H100" s="2">
+        <v>4100</v>
+      </c>
+      <c r="I100" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A101" s="2">
+        <v>100</v>
+      </c>
+      <c r="B101" s="2">
+        <v>2</v>
+      </c>
+      <c r="C101" s="2">
+        <f>VLOOKUP(H101,Sheet1!B:F,5,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="D101" s="2">
+        <v>1</v>
+      </c>
+      <c r="E101" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="F101" s="2">
+        <v>55</v>
+      </c>
+      <c r="H101" s="2">
+        <v>4101</v>
+      </c>
+      <c r="I101" s="7" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
